--- a/Kiem Thu Chuc Nang/Kiểm thử bảng quyết định.xlsx
+++ b/Kiem Thu Chuc Nang/Kiểm thử bảng quyết định.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\test-and-qa\Kiem Thu Chuc Nang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A68FED-2709-4CB0-98B8-298D24794CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09B336A-D0A7-4E49-9FD9-226F786F4400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D5781FE-B2A5-4FB8-B8A1-01703D2F03AA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
   <si>
     <t>Điều kiện</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>TC9</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -285,15 +291,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31796490-8828-422B-BE47-EF6AE53AAFC7}">
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -638,830 +641,863 @@
     <col min="17" max="18" width="11.109375" customWidth="1"/>
     <col min="19" max="19" width="17.109375" customWidth="1"/>
     <col min="20" max="20" width="16.109375" customWidth="1"/>
+    <col min="21" max="21" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="2"/>
+      <c r="N2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>-1</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>50</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>50</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>3</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>3</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="U3" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="1">
         <v>500</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="1">
         <v>50</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>50</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>3</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>0</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="S4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="T4" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="U4" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>500</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="1">
         <v>50</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>5</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>3</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>3</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="T5" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="U5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>960</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="1">
         <v>90</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>50</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>3</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>3</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
+      <c r="U6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>820</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="1">
         <v>85</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>50</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>3</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>3</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T7" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2" t="s">
+      <c r="U7" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <v>650</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="1">
         <v>75</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>50</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>3</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
+      <c r="U8" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>500</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="1">
         <v>55</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>50</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>3</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>3</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
+      <c r="U9" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>500</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
         <v>55</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>50</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>5</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>4</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="S10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
+      <c r="U10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="1">
         <v>500</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="1">
         <v>25</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="1">
         <v>50</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="1">
         <v>3</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="1">
         <v>1</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="T11" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="U11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="2"/>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="2"/>
+      <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2" t="s">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="U1:U2"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:R1"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="A2:A11"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="A12:K12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
